--- a/www/download/COUNTRY.IRL.EXI382.xlsx
+++ b/www/download/COUNTRY.IRL.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>Irlanda</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.03441472392638</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.03441472392638</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.03441472392638</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.03441472392638</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.03441472392638</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.03441472392638</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.03441472392638</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.03441472392638</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.03441472392638</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.03441472392638</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.03441472392638</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.03441472392638</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.03441472392638</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.03441472392638</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.03555337423313</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.03555337423313</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.03555337423313</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.03555337423313</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.03555337423313</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.03555337423313</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.03555337423313</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.03555337423313</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.03555337423313</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.03555337423313</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.03555337423313</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.03555337423313</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.03555337423313</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3.694</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>1.191</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>1.286</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>1.363</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>1.412</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>1.577</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1.656</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>1.712</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>1.716</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>1.785</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>1.824</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>1.934</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2.025</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2.101</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>2.092</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>1.872</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>1.843</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>1.752</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>1.884</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>1.964</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2.792</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>2.84</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2.968</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>3.271</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>3.487</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2.886</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0.921</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>1.017</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>1.081</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>1.273</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>1.399</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>1.407</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>1.469</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>1.496</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>1.601</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>1.691</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>1.739</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>1.727</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>1.538</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>1.555</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>1.462</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>1.565</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>1.619</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2.077</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2.309</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2.426</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>2.607</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2.776</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>6740.67</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2467.074</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2701.785</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2818.018</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2909.62</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>3221.355</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3350.649</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>3437.317</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>3405.903</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>3482.123</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>3537.096</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>3776.972</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>3934.234</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>4047.793</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>3963.095</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>3440.41</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>3414.197</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>3352.109</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>3178.049</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>3442.42</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>3597.922</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>4595.324</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>5098.67</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>5204.554</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>5415.836</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>6004.651</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>6388.714</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5197.415</t>
+          <t>10482195823.2659</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>945.711</t>
+          <t>6371830251.27398</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1199.045</t>
+          <t>6422517827.47247</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1261.275</t>
+          <t>6768082103.27941</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1343.094</t>
+          <t>6943013378.44475</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1604.064</t>
+          <t>8030323484.26126</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1692.979</t>
+          <t>7986315869.54898</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1846.39</t>
+          <t>7195940872.32701</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1814.813</t>
+          <t>6860337034.30539</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1919.615</t>
+          <t>7972897555.07112</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1921.2</t>
+          <t>8944854359.55774</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2150.668</t>
+          <t>9408471691.59139</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>3125.051</t>
+          <t>8624747374.5525</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>3184.546</t>
+          <t>9627738768.18106</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2609.114</t>
+          <t>7104384193.51475</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1933.484</t>
+          <t>5826406740.79282</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2020.989</t>
+          <t>5446348248.55798</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2021.051</t>
+          <t>5647779750.02806</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>1886.364</t>
+          <t>6207572332.61485</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2749.425</t>
+          <t>5976402930.1242</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>2857.729</t>
+          <t>8190583958.6214</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>3708.718</t>
+          <t>9773539643.00387</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>4108.133</t>
+          <t>9065625263.89013</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>4096.028</t>
+          <t>11679080089.7255</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>4313.811</t>
+          <t>12525512584.568</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>4680.31</t>
+          <t>14304585931.6387</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>4987.182</t>
+          <t>16755139149.9895</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1744616044.17095</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1599580738.32057</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1600614834.00857</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1734589523.10794</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2125985600.38444</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2338253350.85423</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2430833376.19845</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1853791291.60175</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1937586953.4156</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2293476524.31854</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2527715439.22182</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2430708275.33551</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2177353779.34404</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2097499372.10171</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>2600836162.43788</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1966309123.98858</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>2194838553.97876</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1902482588.73317</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2430984748.37875</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2149819475.08175</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>2816821362.18799</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>3824225725.09102</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2984211376.77299</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>2941219194.96519</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>3257941543.12391</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>3900213802.95099</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>3992776943.3414</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>86602712.0031154</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>12746826.6600731</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>10613221.2921448</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>11447600.7847715</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>68117834.9537345</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>8212346.76727002</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>7097049.88690405</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>6642642.00062495</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>31950549122.8739</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>5894651.45210872</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>7086620.83941706</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>5602859.67157403</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>5059335.45116259</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>5900659.94366906</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>4487156.14637979</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>4179520.49511903</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>136680838.330602</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>3512324.29259493</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>3487305.9410599</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2827863.31067049</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>2619349.35478367</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2752475.949391</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>1873494.00525099</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>2495284.03911822</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2190791.94857388</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>2357360.84469069</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2632741.75028178</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16051.6987961889</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>11799.2543524531</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>13381.3488799703</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>14615.3184967678</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>15858.2054720177</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>20072.1514343947</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20742.9412642792</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>20525.2675909375</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>18403.0573305831</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>18660.0045301599</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>20496.2662860069</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>23136.1335279651</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>25011.3247971392</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>25638.7471389746</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>24729.936456772</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>24917.5542916252</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>24252.1050099342</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>26167.8481149758</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>25396.5798136919</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>28023.1966713648</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>33715.0028311715</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>43984.907563208</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>53006.9258843928</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>52439.29083669</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>58004.12774496</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>62554.3279847588</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>64249.4647145709</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>39073.4608399087</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>48419.9995887222</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>53156.7653123529</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>57589.211441284</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>62315.5921947168</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>86155.8427624015</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>86034.5961197658</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>75144.5963139262</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>65809.7145380908</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>74741.3045576125</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>89893.7448884293</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>101143.986383149</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>96061.6785677407</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>107748.930163702</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>79676.7280092095</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>75355.0143467799</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>73331.3253762435</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>83933.6265934181</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>90115.1987381898</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>89802.8578199419</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>139028.177267181</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>151210.71038359</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>148287.254230723</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>185796.116499534</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>212305.819215127</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>230653.681033465</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>265244.913836706</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1.97911699327633</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.408775701442012</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-0.25088473846189</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-0.27286831656878</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-0.368248778469255</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-0.313990505171403</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.303539676319841</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-0.00399251611322737</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>-0.0633643580225822</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-0.163010835452051</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>-0.239946091166034</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-0.115209331443216</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.435251831671204</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.518258380601629</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.00318273296568083</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>-0.0166937759624766</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>-0.0792083561968689</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.0623229941595684</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>-0.224032976242554</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.278909522950799</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>0.0145225677688301</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>-0.0302040834196182</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>0.37662279869272</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>0.392629124757075</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>0.324091023528419</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>0.200013764410381</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>0.249050962343898</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>604.610832234042</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1736.97550040254</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1573.54977782999</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1604.91258614729</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1881.07025339296</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1837.09408458075</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1814.32555321532</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1325.36733509863</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1376.90943250117</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1561.56909124965</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1689.42349901174</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1518.71807268681</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1287.6131161111</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1206.36071323537</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1505.89784172189</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1278.81706815028</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1411.2902224662</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1235.45852895189</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1663.34912649926</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1373.4746519059</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>1739.89768972691</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>1841.18453641421</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>1292.17355144875</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>1278.57590680498</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>1342.88238573946</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>1495.92409359138</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1438.09235313148</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>4149389116.60139</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>2575550518.6032</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>2975825040.3574</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>3422230305.08354</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>4572073712.46738</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>4836192194.91567</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>5866401235.55859</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>6982957275.18611</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>6823033641.22811</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>8050794807.47656</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>7316803590.32306</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>6162146374.4587</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>5658710118.75336</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>5302206925.87231</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>6830329138.02529</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>6824921651.89754</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>7072579463.68214</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>6873951494.29392</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>7788608869.55275</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>7642976003.80825</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>12370858424.024</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>9532038166.82955</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>10687933917.5665</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>14281361903.5388</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>8486225858.69529</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>9253773338.3091</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>10924877731.6118</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>7202706161.72013</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>3640591521.25957</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>3712734366.63055</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>3971506305.13686</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>4582516777.76501</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>4071988652.41218</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>6017251246.01515</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>7426218020.20336</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>7622661207.81037</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>7967239242.77111</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>6469867713.31256</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>5561425078.24289</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>4765584731.71611</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>5056389499.46674</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>6631720720.42284</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>5380089321.51909</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>5266467508.56863</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>5256320406.12757</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>6026100631.96222</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>5581839416.8584</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>12228330770.9171</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>11539315535.2768</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>10787886082.2609</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12695387133.4088</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>9986895977.71541</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10965827863.6759</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>11053376803.604</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-3053317045.11874</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-1065041002.65637</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-736909326.273152</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-549276000.053315</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-10443065.2976385</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>764203542.503491</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-150850010.45656</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-443260745.017253</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>-799627566.582258</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>83555564.7054427</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>846935877.010498</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>600721296.215809</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>893125387.037253</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>245817426.405564</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>198608417.602445</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1444832330.37846</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>1806111955.11351</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1617631088.16635</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>1762508237.59052</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2061136586.94985</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>142527653.106918</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>-2007277368.44724</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>-99952164.6943908</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>1585974770.13002</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>-1500670119.02012</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>-1712054525.36682</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>-128499071.992153</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>1801.20640462738</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>1026.9421218379</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>1178.77015336235</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>1166.98279052523</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>1188.36843036615</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>1260.26398491584</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>1263.60576205352</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>1320.07578465731</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>1289.66245025549</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>1307.01640906894</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.351</t>
+          <t>1284.05293409983</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.395</t>
+          <t>1343.74757888184</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>1848.04908338232</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.424</t>
+          <t>1831.56726289815</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>1510.69071242569</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>1257.46878251759</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.361</t>
+          <t>1299.50424382794</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.385</t>
+          <t>1312.45600363615</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.402</t>
+          <t>1290.70407115918</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.431</t>
+          <t>1756.54981185399</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0.596</t>
+          <t>1765.1654718368</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0.642</t>
+          <t>1785.57324508545</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>0.683</t>
+          <t>1778.83557079209</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>0.744</t>
+          <t>1780.5820460293</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>0.854</t>
+          <t>1778.09851261205</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.906</t>
+          <t>1795.12950282278</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>0.927</t>
+          <t>1796.25063761828</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>1824.69779095716</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>2071.9526329053</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>2101.24825011662</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>2067.66307139187</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>2059.90796460163</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>2043.2291005968</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>2023.46095778664</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>2007.30962391965</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>1984.44502709295</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>1950.33213845573</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>1939.09105860385</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>1952.93278179963</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>1942.54382066838</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>1926.60304616892</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>1894.22378357726</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>1839.98823403528</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>1823.336181576</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>1819.22772169722</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>1813.95490867524</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>1827.09509355727</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>1831.57990755568</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>1838.28652598153</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>1826.37419907079</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>1832.66749812217</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>1824.51634722732</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>1835.66821181159</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>1832.08564879618</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>34605.5328518192</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>46457.7376326872</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>60633.2023778281</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>76173.4240083133</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>90431.6807244072</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>116637.616482629</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>132194.058901563</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>137999.650764346</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>130861.242437197</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>137342.424458513</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>149422.674811192</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>163110.097181037</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>177237.582813164</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>172405.1152944</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>175881.407921198</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>198751.046432987</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>201956.901105489</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>209307.311602977</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>215129.481915781</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>250575.109124028</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>390516.525055462</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>401481.198467725</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>439789.48549547</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>491696.460837912</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>555376.851467798</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>581351.384770044</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>606741.399423904</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2662018487.93785</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2203229802.23811</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2388987668.35344</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2728108271.93585</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2747860830.74947</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>3397931604.04306</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3266502939.66908</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2862953199.07328</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2385861471.85583</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2698123482.93205</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2953511152.77118</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>3164744560.50306</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2775830984.90751</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>3093314121.11844</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2371835345.56361</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>2205674185.5115</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>2185906614.20952</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>2118709086.76946</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2367872014.31425</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2449766788.92638</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>3581709417.55678</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>4322966469.26548</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>4232508219.79583</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>5547819261.69211</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>6016722950.30044</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>6838927805.41568</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>7777490291.14305</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>26998.9517389384</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>37977.9014408742</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>49240.9966996372</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>64621.3546442054</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>74622.0841823741</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>97065.7933126385</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>107494.478058865</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>108069.322036534</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>102478.87172863</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>108472.010424856</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>125406.426740307</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>143658.83219377</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>155836.166953713</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>151424.474236221</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>146355.856870052</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>162316.116521708</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>160222.988693262</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>169625.496083099</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>170767.334200299</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>204305.912724151</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>291472.929856799</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>345902.687542444</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>353874.278787118</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>369496.097488555</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>497784.224171847</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>522503.279996065</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>547080.140102192</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>6740.67</t>
+          <t>2502079809.69803</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2467.074</t>
+          <t>3056202942.54943</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2701.785</t>
+          <t>3232331734.08975</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2818.018</t>
+          <t>3973948110.21578</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2909.62</t>
+          <t>4419760609.05921</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3221.355</t>
+          <t>5197739832.39629</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3350.649</t>
+          <t>5149380759.10725</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>3437.317</t>
+          <t>4837562293.17789</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>3405.903</t>
+          <t>4387364474.3533</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>3482.123</t>
+          <t>5454377632.41552</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>3537.096</t>
+          <t>6253583220.14348</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>3776.972</t>
+          <t>6432704158.25107</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>3934.234</t>
+          <t>5776861832.84419</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>4047.793</t>
+          <t>5520347645.39371</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>3963.095</t>
+          <t>4856256993.80565</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>3440.41</t>
+          <t>4538095512.5113</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>3414.197</t>
+          <t>4445908446.16043</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>3352.109</t>
+          <t>4666103364.99142</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>3178.049</t>
+          <t>5074639075.4136</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>3442.42</t>
+          <t>5174045318.42581</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>3597.922</t>
+          <t>6378530259.96557</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>4595.324</t>
+          <t>7960540528.02958</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>5098.67</t>
+          <t>6644852557.00745</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>5204.554</t>
+          <t>7683722959.9163</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>5415.836</t>
+          <t>9246619105.34996</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>6004.651</t>
+          <t>10382002998.7332</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>6388.714</t>
+          <t>12889268806.6505</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>5197.415</t>
+          <t>7606.58111288088</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>945.711</t>
+          <t>8479.83619181296</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1199.045</t>
+          <t>11392.205678191</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1261.275</t>
+          <t>11552.0693641078</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1343.094</t>
+          <t>15809.5965420332</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1604.064</t>
+          <t>19571.82316999</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1692.979</t>
+          <t>24699.5808426985</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1846.39</t>
+          <t>29930.3287278126</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1814.813</t>
+          <t>28382.3707085678</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1919.615</t>
+          <t>28870.4140336569</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1921.2</t>
+          <t>24016.2480708849</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2150.668</t>
+          <t>19451.2649872674</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>3125.051</t>
+          <t>21401.4158594511</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>3184.546</t>
+          <t>20980.6410581782</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2609.114</t>
+          <t>29525.5510511456</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1933.484</t>
+          <t>36434.9299112788</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>2020.989</t>
+          <t>41733.9124122263</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2021.051</t>
+          <t>39681.8155198785</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>1886.364</t>
+          <t>44362.1477154817</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2749.425</t>
+          <t>46269.1963998777</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>2857.729</t>
+          <t>99043.5951986633</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>3708.718</t>
+          <t>55578.5109252808</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>4108.133</t>
+          <t>85915.2067083526</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>4096.028</t>
+          <t>122200.363349357</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>4313.811</t>
+          <t>57592.6272959507</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>4680.31</t>
+          <t>58848.1047739783</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>4987.182</t>
+          <t>59661.2593217122</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>7268.346</t>
+          <t>159938678.239825</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4060.48</t>
+          <t>-852973140.311315</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>4166.966</t>
+          <t>-843344065.736314</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>4420.822</t>
+          <t>-1245839838.27994</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>4617.124</t>
+          <t>-1671899778.30975</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>5312.787</t>
+          <t>-1799808228.35323</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>5305.014</t>
+          <t>-1882877819.43817</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>4916.627</t>
+          <t>-1974609094.10461</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>4688.033</t>
+          <t>-2001503002.49746</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>5409.47</t>
+          <t>-2756254149.48347</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>6088.031</t>
+          <t>-3300072067.37231</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>6329.19</t>
+          <t>-3267959597.74801</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>5963.367</t>
+          <t>-3001030847.93668</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>6461.351</t>
+          <t>-2427033524.27527</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>4860.65</t>
+          <t>-2484421648.24204</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>4054.122</t>
+          <t>-2332421326.99981</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>3788.631</t>
+          <t>-2260001831.95091</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>3884.285</t>
+          <t>-2547394278.22196</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>4195.656</t>
+          <t>-2706767061.09935</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>4142.227</t>
+          <t>-2724278529.49943</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>5452.664</t>
+          <t>-2796820842.40879</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>6675.237</t>
+          <t>-3637574058.7641</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>6473.412</t>
+          <t>-2412344337.21163</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>7881.028</t>
+          <t>-2135903698.22419</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>8577.205</t>
+          <t>-3229896155.04952</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>9723.635</t>
+          <t>-3543075193.31752</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>11333.006</t>
+          <t>-5111778515.50746</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>17912.5016863488</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>18388.2341212358</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>22776.1557161722</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>26363.3800090192</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>31653.5333676954</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>35687.2318533863</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>41217.9086470655</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>43404.9473048131</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>50402.7052946447</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>53223.0842045746</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>58970.4836366888</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>66738.1258493155</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>66336.4043984932</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>65997.3022845293</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>69801.0400756438</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>51419.2863095903</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>52105.3110959803</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>55546.5211701997</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>60858.6454534239</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>64110.8465870812</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>101470.258914234</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>106505.472995391</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>113834.064599545</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>119142.862254196</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>141363.955392526</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>148389.824735687</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>142207.185061324</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>4306.172</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>1552.723</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>1616.764</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>1717.642</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>1766.873</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>1870.864</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1925.501</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>1965.525</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>1918.428</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>1990.523</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>2039.476</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>2152.136</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>2245.603</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>2290.911</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>2205.047</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>1926.611</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>1801.214</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>1760.799</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>1749.44</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>1864.951</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>1986.256</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>2842.975</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>3240.608</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>3296.316</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>3422.099</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>3879.469</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>4058.546</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>30766.9413116375</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>34391.0710239077</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>41014.8621737497</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>45414.6842436254</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>48958.2209374259</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>57494.291653001</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>64562.826266359</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>66445.4305023572</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>77508.7177038802</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>80213.8704604182</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>87871.2669886663</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>95331.1175449154</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>102645.076309862</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>101878.009337695</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>105170.009295505</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>89002.2347156742</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>93184.080264209</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>88398.8396526396</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>92157.3318483547</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>96121.8311015263</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>123592.380540375</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>123333.979391392</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>144746.728988985</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>154141.878912654</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>180420.917449309</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>188950.444074025</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>185097.649061733</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1561.965</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>1433.131</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>1480.423</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>1614.055</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>1979.272</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>2191.536</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2251.69</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>1731.618</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>1835.275</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>2181.589</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>2363.852</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>2272.277</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>2059.12</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>1964.06</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>2463.987</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>1893.092</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>2113.604</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>1781.085</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>2255.156</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>2057.855</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>2731.562</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>3740.267</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2963.352</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>2879.815</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>3265.507</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>3921.026</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>3967.419</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>232.75</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>-34.01</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-19.01</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-21.86</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-32.14</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>-26.81</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>-24.81</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>6.63</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>-1.11</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>-12.01</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>-18.73</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>-5.35</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>51.77</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>62.14</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>5.89</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>2.13</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>-4.38</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>13.47</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>-16.35</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>33.61</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>4.62</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>-0.84</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>38.63</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>42.23</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>32.1</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>19.36</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>25.7</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>80.058</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>10.813</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>8.917</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>10.107</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>63.807</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>7.568</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>6.111</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>6.158</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>30211.98</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>5.022</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>6.249</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>4.759</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>4.302</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>5.015</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>3.87</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>3.675</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>129.057</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>3.534</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>3.287</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>2.91</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>2.849</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>2.42</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2.463</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>2.69</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2.315</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>2.529</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>2.764</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>26023.3834009964</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>29620.6440203738</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>36303.7024090073</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>39749.4054665967</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>47536.2708009883</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>55219.4126071153</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>62264.0798233344</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>74243.0284354401</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>72332.5990062752</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>81836.8082316639</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>89880.2112643242</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>95805.4178666772</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>101903.247966637</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>91988.6727543345</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>68606.2414684269</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>85686.1970813877</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>83734.6028674717</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>92166.7326742043</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>93259.796095255</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>103309.090479281</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>141118.962393782</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>142607.887596797</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>152923.05940686</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>173253.3778606</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>174929.330962326</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>178962.17206489</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>195302.977187976</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>5197415303.93221</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>945711000.000445</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1199045000.0001</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1261274999.99964</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1343093999.99964</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>1604064000.00078</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1692978999.99971</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1846389999.99947</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>1814812999.99949</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>1919614999.99971</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>1921200000.00051</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2150668000.00062</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>3125050999.99975</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>3184546000.00007</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2609113929.4304</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1933483999.99974</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>2020989000.00059</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>2021050999.99947</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>1886363999.9992</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2749424599.30714</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>2857728841.31306</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>3708718492.27492</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>4108133417.38389</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>4096027513.20308</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>4313811152.4307</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>4680310247.68454</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>4987181883.50511</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>6740669730.12152</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2467074000.00028</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2701784999.99984</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2818018000.00005</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2909619999.99953</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>3221355000.00074</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3350648999.99979</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>3437316999.99909</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>3405902999.99969</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>3482122999.99943</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>3537095999.99993</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>3776972000.00107</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>3934233999.99976</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>4047793000.00009</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>3963095000.00046</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>3440410000.00041</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>3414197000.00028</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>3352108999.99956</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>3178048999.99924</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>3442419646.67317</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>3597922239.81212</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>4595324465.87109</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>5098669801.95822</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>5204553525.31393</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>5415835869.96329</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>6004651096.48624</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>6388714451.43984</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>4306172180.8343</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1552722975.30023</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1616764135.89572</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1717642472.88845</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1766872926.54309</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>1870864051.41184</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1925500769.12578</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1965525389.9568</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1918427646.06387</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1990523250.52005</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2039475795.23571</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>2152136425.84888</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>2245602628.37888</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2290910540.10904</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2205047497.05344</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1926611089.48485</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1801213996.43337</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1760798963.22697</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>1749439699.42895</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>1864950835.23946</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>1986256072.55987</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>2842974791.0868</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>3240608432.27309</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>3296315816.86825</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>3422098530.84714</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>3879468803.81271</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>4058546141.50192</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>3694129.38598761</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1190699.99999997</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1285799.99999995</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1362900.00000003</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1412499.99999987</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>1576599.99999992</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1655900.00000044</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1712399.99999954</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>1716300.00000004</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1785400.00000029</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>1824100.00000033</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>1934000.0000003</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2025300.00000005</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2100999.99999959</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2092200.00000006</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1869800.00000067</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>1872499.99999957</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1842600.00000014</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>1752000.00000012</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>1884094.40691505</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>1964381.80227348</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>2499786.84003979</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2791689.5697236</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>2839878.77268885</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2968367.96129211</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>3271098.26157547</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>3487126.519242</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2885519.0002544</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>920899.999999925</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1017199.99999993</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1080799.99999997</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1130199.99999985</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1272799.99999992</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1339800.00000031</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1398699.99999946</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>1407199.99999997</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>1468700.00000012</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>1496200.00000027</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>1600500.00000018</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>1691000.00000013</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>1738699.99999948</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1727100</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1537600.00000056</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>1555199.99999952</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1539900.00000013</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>1461500.00000004</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>1565241.46412062</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>1618958.04495845</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>2077046.40651549</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2309450.90419717</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>2300386.84391838</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2426081.07584189</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>2607227.07767039</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>2776439.86816774</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>6740669730.12152</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2467074000.00028</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2701784999.99984</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2818018000.00005</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2909619999.99953</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>3221355000.00074</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3350648999.99979</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>3437316999.99909</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>3405902999.99969</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>3482122999.99943</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>3537095999.99993</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>3776972000.00107</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>3934233999.99976</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>4047793000.00009</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>3963095000.00046</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>3440410000.00041</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>3414197000.00028</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>3352108999.99956</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>3178048999.99924</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>3442419646.67317</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>3597922239.81212</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>4595324465.87109</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>5098669801.95822</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>5204553525.31393</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>5415835869.96329</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>6004651096.48624</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>6388714451.43984</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>5197415303.93221</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>945711000.000445</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1199045000.0001</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1261274999.99964</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1343093999.99964</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>1604064000.00078</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1692978999.99971</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>1846389999.99947</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>1814812999.99949</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>1919614999.99971</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>1921200000.00051</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>2150668000.00062</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>3125050999.99975</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>3184546000.00007</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>2609113929.4304</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>1933483999.99974</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>2020989000.00059</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>2021050999.99947</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>1886363999.9992</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2749424599.30714</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>2857728841.31306</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>3708718492.27492</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>4108133417.38389</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>4096027513.20308</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>4313811152.4307</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>4680310247.68454</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>4987181883.50511</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>113201.236398127</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>124899.19003776</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>155972.999063728</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>177343.415722674</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>206448.424850785</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>249382.509911672</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>285418.331351172</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>302846.657371232</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>325216.500143744</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>348402.052304229</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>384739.164044152</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>433270.132173107</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>460739.31013415</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>466026.586009802</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>406463.556865125</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>403663.296410514</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>394136.471643472</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>421338.553094245</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>440380.873585847</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>471113.827716497</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>644127.424012598</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>695019.948547931</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>740500.192356069</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>804243.489076136</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>925141.051042164</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>982626.573284536</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>1006039.8106133</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>32302.7984823735</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>36093.4360236444</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>44066.9872558084</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>48680.067156549</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>53933.4730465876</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>63082.0730331958</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>70444.5401210462</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>73023.8720282549</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>86318.7917360232</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>89257.6176575723</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>97214.3587173002</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>107522.502879033</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>114716.473360745</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>114014.868434016</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>118175.562837178</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>98850.8091078869</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>103757.493106292</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>100582.346682841</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>104671.793776018</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>111413.729096065</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>144224.986032919</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>149941.781566274</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>172755.730351576</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>182402.52999974</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>214625.685206984</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>224410.128928064</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>218437.51193459</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
